--- a/VT_KiNESYS_NewElc_V6.xlsx
+++ b/VT_KiNESYS_NewElc_V6.xlsx
@@ -790,14 +790,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1259,28 +1252,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1289,118 +1285,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2629,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2">
-        <v>2105</v>
+        <v>2200</v>
       </c>
       <c r="L25" t="s">
         <v>20</v>
@@ -2676,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2">
-        <v>2105</v>
+        <v>2200</v>
       </c>
       <c r="L26" t="s">
         <v>20</v>
